--- a/TAI_Metrics_Book.xlsx
+++ b/TAI_Metrics_Book.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mgh2v\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moesanjari/TrustAtLas-NIST-RMF-Mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{8A0E7AAD-E785-4D97-99F8-03556D16D259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B09D1531-8772-41EE-9889-05BF6E26ADAA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FDDCD5-265A-FC42-9884-28CDB373A796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="6" xr2:uid="{092FAFF7-1428-4AC3-8AB7-4C9FCB914AE8}"/>
+    <workbookView xWindow="-31400" yWindow="-5580" windowWidth="32000" windowHeight="16520" activeTab="6" xr2:uid="{092FAFF7-1428-4AC3-8AB7-4C9FCB914AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Validity and Reliability" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="382">
   <si>
     <t>Metric</t>
   </si>
@@ -313,176 +313,39 @@
     <t>F6</t>
   </si>
   <si>
-    <t>refers to the degree to which it contains the necessary information required to accurately model the underlying patterns by the learning algorithm - where γ(di) is 0 if d_i is a missing data, and 1 otherwise</t>
-  </si>
-  <si>
     <t>Data correctness</t>
   </si>
   <si>
-    <t>refers to the accuracy of the data items to faithfully represent the real-world phenomena or objects they meant to capture - where ω is the data value to be assessed, ω_m is the corresponding real value and d is a domain-specific distance measure - 1 → perfectly correct data Closer to 0 → increasingly incorrect or noisy data</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Student’s </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-test</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Numeric - [-∞,-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>∞]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">a parametric hypothesis test that evaluates whether the means of two groups are statistically different by comparing their standardized mean difference to a </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>-distribution under the assumption of approximately normal data -t=0 → no difference between the means (perfect agreement with the null hypothesis). ∣t∣ increases → stronger evidence against the null hypothesis.</t>
-    </r>
-  </si>
-  <si>
-    <t>Chi-square test</t>
-  </si>
-  <si>
-    <r>
-      <t>Numeric - [0,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>∞]</t>
-    </r>
-  </si>
-  <si>
-    <t>a non-parametric statistical hypothesis test that assesses whether observed categorical data significantly deviate from expected frequencies under a specified null hypothesi, where 𝑂_𝑖 is the observed frequency and 𝐸_𝑖 is the expected frequency for category - χ2=0 → perfect agreement between observed and expected counts, Larger χ 2→ greater discrepancy and stronger evidence against the null hypothesis</t>
-  </si>
-  <si>
-    <t>Kolmogorov–Smirnov (KS) test</t>
-  </si>
-  <si>
-    <t>a non-parametric hypothesis test that quantifies the maximum distance between empirical cumulative distribution functions to determine whether two samples, or a sample and a reference distribution, are drawn from the same underlying distribution -where F_n_(x) and G_m(x) are the empirical cumulative distribution functions (ECDFs) of two samples of sizes 𝑛 and 𝑚- 𝐷=0 → distributions are identical, Larger D → stronger evidence that the distributions differ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Specificity </t>
   </si>
   <si>
-    <t>measures the ability of a model to correctly identify negative instances by quantifying the proportion of true negatives among all actual negatives - 1 → no false positives (perfect negative classification), 0 → all negatives are misclassified as positives</t>
-  </si>
-  <si>
     <t>Specificity = T N/(FP+T N)</t>
   </si>
   <si>
     <t>Availability</t>
   </si>
   <si>
-    <t>measures the proportion of time a system remains operational by comparing uptime to the total operational time, including downtime- 1 → system is always available (no downtime), 0 → system is never available, Values closer to 1 indicate higher reliability and operational readiness</t>
-  </si>
-  <si>
     <t>Availability = Uptime/(Uptime+ Downtime)</t>
   </si>
   <si>
     <t>Mean time to failure (MTTF) / Mean time between failure (MTBF)</t>
   </si>
   <si>
-    <t>Mean Time Between Failures (MTBF) quantifies system reliability by measuring the average operational time elapsed between consecutive failures- Higher MTBF → more reliable system with fewer failures, Lower MTBF → frequent failures and reduced dependability</t>
-  </si>
-  <si>
     <t>Repeatability</t>
   </si>
   <si>
-    <t>measures the degree to which an AI system or measurement process produces consistent outputs when the same input is evaluated multiple times under identical conditions - 1 → perfectly consistent, identical repeated outputs, 0 → highly variable, non-repeatable results</t>
-  </si>
-  <si>
     <t>Reproducibility</t>
   </si>
   <si>
-    <t>measures the extent to which an AI system yields consistent results when experiments are repeated under varying conditions such as different datasets, environments, implementations, or operators - 1 → results are fully reproducible across settings, 0 → results vary substantially and cannot be reliably reproduced</t>
-  </si>
-  <si>
-    <t>Hallucination Detection Accuracy</t>
-  </si>
-  <si>
     <t>F7</t>
   </si>
   <si>
-    <t>GenAI (LLM)</t>
-  </si>
-  <si>
-    <t>The accuracy of the model in distinguishing between factual statements and hallucinated (non-factual) content (e.g., on HaluEval)</t>
-  </si>
-  <si>
-    <t>Measures the model’s ability to produce factually correct answers on truthfulness benchmarks (e.g., TruthfulQA), thereby indicating its capacity to reduce the generation of false beliefs.</t>
-  </si>
-  <si>
-    <t>Macro F1 Score</t>
-  </si>
-  <si>
-    <t>Used for zero-shot fact-checking tasks in misinformation generation integrating external knowledge</t>
-  </si>
-  <si>
-    <t>Retrieval Rate</t>
-  </si>
-  <si>
     <t>F8</t>
   </si>
   <si>
     <t>Memory</t>
   </si>
   <si>
-    <t>Measures the accuracy of the agent in successfully retrieving the correct, relevant information from its long-term memory (Vector DB)</t>
-  </si>
-  <si>
     <t>System design</t>
   </si>
   <si>
@@ -525,24 +388,9 @@
     <t>After the model's architecture is designed, models are trained using automation with no human intervention- 0 implies this is false, 1 implies this is true</t>
   </si>
   <si>
-    <t>Refuse to Answer (RtA) Percentage</t>
-  </si>
-  <si>
     <t>Numeric [0,1]</t>
   </si>
   <si>
-    <t>Measures the percentage of instances where LLMs refuse to answer in contexts like jailbreak</t>
-  </si>
-  <si>
-    <t>Toxicity Score</t>
-  </si>
-  <si>
-    <t>Obtained from Perspective API to quantify toxicity in outputs after successful jailbreaks</t>
-  </si>
-  <si>
-    <t>Used for evaluating implicit ethics on datasets like ETHICS and SOCIAL CHEMISTRY 101, and for low-ambiguity scenarios in explicit ethics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Scope </t>
   </si>
   <si>
@@ -681,32 +529,12 @@
     <t>comparing predictive accuracy, as measured by Shapley–Lorenz values, in different ordered subset the data, possibly altered artificially by anomalous or cyber manipulated ones; LZ(V_{G}^{SL_*}) is the gini coefficient on the vector V_{G}^{SL_*}</t>
   </si>
   <si>
-    <t>Robustness Rate</t>
-  </si>
-  <si>
-    <t>Measures the stability of the model's performance when subjected to adversarial inputs or noise compared to its performance on clean data.</t>
-  </si>
-  <si>
-    <t>Acc(adv) - ASR</t>
-  </si>
-  <si>
     <t>Attack Success Rate (ASR)</t>
   </si>
   <si>
-    <t>Measures the success rate of attacks in robustness evaluations</t>
-  </si>
-  <si>
-    <t>ASR = count of samples that were correctly classified in the
-benign set but misclassified in the adversarial set / number of samples correctly
-classified within the benign set</t>
-  </si>
-  <si>
     <t>OOD Robustness</t>
   </si>
   <si>
-    <t>Used for OOD detection in robustness</t>
-  </si>
-  <si>
     <t>Data Usage Report</t>
   </si>
   <si>
@@ -914,12 +742,6 @@
     <t>Fidelity</t>
   </si>
   <si>
-    <t>XAI Method</t>
-  </si>
-  <si>
-    <t>is defined as the model's confidence score (f(x)) in its original prediction after the top-ranked features identified by the explanation method have been modified or masked (f(x\S)). The value range is in the interval of [0,1], score closer to 0 is better.</t>
-  </si>
-  <si>
     <t>Faithfulness</t>
   </si>
   <si>
@@ -929,18 +751,9 @@
     <t>Monotonicity</t>
   </si>
   <si>
-    <t>XAI</t>
-  </si>
-  <si>
-    <t>measures the extent to which changes in an input variable consistently induce changes in the same direction in the model output, indicating whether the model behavior aligns with expected monotonic relationships, where ρ(x,y) is a rank-based correlation coefficient (e.g., Spearman’s, ρ between an input feature x and the model output y- -1 → perfectly increasing monotonic relationship, −1 → perfectly decreasing monotonic relationship, 0 → no monotonic relationship.</t>
-  </si>
-  <si>
     <t>Sensitivity</t>
   </si>
   <si>
-    <t xml:space="preserve">measures the ability of a model to correctly identify positive instances by computing the proportion of true positives among all actual positives, 1 → all positives correctly detected, 0 → no positives detected, </t>
-  </si>
-  <si>
     <t>Legal &amp; Privacy Frameworks</t>
   </si>
   <si>
@@ -1055,45 +868,9 @@
     <t>evaluates the trustworthiness level (heruistic proposed by the authors, Sanchez et al) of the aggregation task</t>
   </si>
   <si>
-    <t>Pearson’s Correlation Coefficient</t>
-  </si>
-  <si>
-    <t>Numeric [-1,1]</t>
-  </si>
-  <si>
-    <t>Used for agreement on privacy information usage in privacy awareness</t>
-  </si>
-  <si>
-    <t>Refuse to Answer (RtA) Percentage,</t>
-  </si>
-  <si>
     <t>Numeric - [0-1]</t>
   </si>
   <si>
-    <t>The rate at which the model correctly refuses to answer questions that require disclosing private information</t>
-  </si>
-  <si>
-    <t>Total Disclosure (TD)</t>
-  </si>
-  <si>
-    <t>The ratio of successful privacy leaks (correctly generated sensitive info) relative to the total number of attempts.</t>
-  </si>
-  <si>
-    <t>Chunk Recovery Rate (CRR)</t>
-  </si>
-  <si>
-    <t>LLM Agent</t>
-  </si>
-  <si>
-    <t>Used in data theft attacks (e.g., RAG-Thief). It measures the percentage of private text chunks from the database that an attacker successfully extracts verbatim.</t>
-  </si>
-  <si>
-    <t>Semantic Similarity</t>
-  </si>
-  <si>
-    <t>Measures how semantically close the stolen/leaked data is to the original private data, even if it isn't an exact match (using Embedding Cosine Similarity).</t>
-  </si>
-  <si>
     <t>Phases</t>
   </si>
   <si>
@@ -1193,32 +970,242 @@
     <t>the measurement of the concentration of the explanatory variables which may be affected by bias, in terms of the Shapley–Lorenz values; LZ(V_{M}^{SL_*}) is the Gini coefficient computed on the vector V_{M}^{SL_*} and whose elements are align to the sum of the selected predictors' Shapley-Lorenz values in each population</t>
   </si>
   <si>
-    <t xml:space="preserve"> Accuracy</t>
-  </si>
-  <si>
-    <t>The model's accuracy in correctly identifying which part of a text contains a stereotype. Higher is better.</t>
-  </si>
-  <si>
-    <t>Disparagement</t>
-  </si>
-  <si>
-    <t>A statistical measure (Chi-Square test) to determine if the model significantly favors or disparages one demographic group over another in decision</t>
-  </si>
-  <si>
-    <t>CHISQ.DIST.RT(x, deg_freedom)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agreement </t>
-  </si>
-  <si>
-    <t>Percentage of instances where LLMs output agreement with stereotype statements in fairness evaluations</t>
+    <t>Data Representativeness</t>
+  </si>
+  <si>
+    <t>Numeric - [-∞,-∞]</t>
+  </si>
+  <si>
+    <t>Assessment of how well the dataset distribution matches the intended population and the ODD.</t>
+  </si>
+  <si>
+    <t>Student, Chi-square, or Kolmogorov-Smirnov tests</t>
+  </si>
+  <si>
+    <t>refers to the degree to which it contains the necessary information required to accurately model the underlying patterns by the learning algorithm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">refers to the accuracy of the data items to faithfully represent the real-world phenomena or objects they meant to capture </t>
+  </si>
+  <si>
+    <t>Data diversity</t>
+  </si>
+  <si>
+    <t>Quantifies how the dataset fits the environment and application domains described in specifications.</t>
+  </si>
+  <si>
+    <t>measures the ability of a model to correctly identify negative instances by quantifying the proportion of true negatives among all actual negatives</t>
+  </si>
+  <si>
+    <t>Percentage of time that the system is actually available over the scheduled operational time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric </t>
+  </si>
+  <si>
+    <t>Measures the expected time a system operates before failure (MTTF) or the average time between successive failures (MTBF), reflecting system reliability and operational stability over time.</t>
+  </si>
+  <si>
+    <t>Variation in various runs of a test plan under the same conditions.</t>
+  </si>
+  <si>
+    <t>Measures the consistency of system outputs when experiments are repeated under varying conditions, such as different environments, datasets, or implementations.</t>
+  </si>
+  <si>
+    <t>Internal Knowledge</t>
+  </si>
+  <si>
+    <t>Evaluates factual correctness of model responses based solely on internal knowledge without external support.</t>
+  </si>
+  <si>
+    <t>External Knowledge</t>
+  </si>
+  <si>
+    <t>Measures factual accuracy when the model is augmented with external knowledge sources.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hallucination </t>
+  </si>
+  <si>
+    <t>Assesses the tendency of the model to generate incorrect or unsupported information.</t>
+  </si>
+  <si>
+    <t>Persona-based Sycophancy</t>
+  </si>
+  <si>
+    <t>Measures the tendency of the model to align responses with a user’s persona even when it contradicts factual correctness.</t>
+  </si>
+  <si>
+    <t>Preference-based Sycophancy</t>
+  </si>
+  <si>
+    <t>Evaluates whether the model favors user preferences over objective truth.</t>
+  </si>
+  <si>
+    <t>Adversarial Factuality</t>
+  </si>
+  <si>
+    <t>Tests the model’s ability to maintain factual correctness under adversarial or misleading inputs.</t>
+  </si>
+  <si>
+    <t>Retrieval Success Rate (RSR)</t>
+  </si>
+  <si>
+    <t>LLM-based Agent (RAG)</t>
+  </si>
+  <si>
+    <t>Measures how accurately the agent retrieves relevant and correct information from memory or external knowledge sources</t>
+  </si>
+  <si>
+    <t>Chunk Recovery Rate</t>
+  </si>
+  <si>
+    <t>Measures the proportion of relevant chunks successfully retrieved</t>
+  </si>
+  <si>
+    <t>Recovered Relevant Chunks / Total Relevant Chunks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semantic Similarity </t>
+  </si>
+  <si>
+    <t>LLM-based Agent</t>
+  </si>
+  <si>
+    <t>Measures similarity between generated outputs and ground truth using embedding-based similarity</t>
+  </si>
+  <si>
+    <t>Jailbreak Robustness</t>
+  </si>
+  <si>
+    <t>Numeric (evaluation-dependent)</t>
+  </si>
+  <si>
+    <t>Evaluates whether the model can resist jailbreak attacks that attempt to bypass safety mechanisms.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toxicity </t>
+  </si>
+  <si>
+    <t>Measures the extent to which the model generates harmful, offensive, or toxic content.</t>
+  </si>
+  <si>
+    <t>Misuse</t>
+  </si>
+  <si>
+    <t>Assesses whether the model can be exploited to generate harmful or malicious outputs.</t>
+  </si>
+  <si>
+    <t>Exaggerated Safety</t>
+  </si>
+  <si>
+    <t>Measures over-restrictiveness, where the model incorrectly refuses benign or safe prompts.</t>
+  </si>
+  <si>
+    <t>Measures the proportion of adversarial attempts that successfully induce harmful or unintended behavior in the agent</t>
+  </si>
+  <si>
+    <t>successful attacks / total attempts</t>
+  </si>
+  <si>
+    <t>Local Robustness</t>
+  </si>
+  <si>
+    <t>Measures the stability of model predictions under small input perturbations.</t>
+  </si>
+  <si>
+    <t>Global Robustness</t>
+  </si>
+  <si>
+    <t>Evaluates the consistency of model performance across varying input distributions and operating conditions.</t>
+  </si>
+  <si>
+    <t>Adversarial Robustness</t>
+  </si>
+  <si>
+    <t>F6, F7</t>
+  </si>
+  <si>
+    <t>Assesses the model’s resistance to adversarially crafted inputs designed to manipulate predictions.</t>
+  </si>
+  <si>
+    <t>Natural Noise Robustness</t>
+  </si>
+  <si>
+    <t>Measures model stability under natural input perturbations such as noise or paraphrasing.</t>
+  </si>
+  <si>
+    <t>Assesses model performance under distribution shifts or unseen data conditions.</t>
+  </si>
+  <si>
+    <t>evaluates the degree to which an explanation function reproduces the predictions of the original model, often assessed over a local input neighborhood.</t>
+  </si>
+  <si>
+    <t>evaluates whether progressively adding important input features leads to a consistent increase in the model’s predicted probability for the target class.</t>
+  </si>
+  <si>
+    <t>Measures the degree to which an explanation changes in response to small input perturbations, typically estimated using Monte Carlo sampling-based approximation</t>
+  </si>
+  <si>
+    <t>Interpretability</t>
+  </si>
+  <si>
+    <t>Design</t>
+  </si>
+  <si>
+    <t>Qualitative</t>
+  </si>
+  <si>
+    <t>Assesses how easily human experts can understand the internal workings of an AI system</t>
+  </si>
+  <si>
+    <t>Usefulness</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>Evaluates how effectively explanations support human decision-making</t>
+  </si>
+  <si>
+    <t>Privacy Awareness</t>
+  </si>
+  <si>
+    <t>Evaluates whether the model correctly identifies and handles sensitive or private information.</t>
+  </si>
+  <si>
+    <t>Privacy Leakage</t>
+  </si>
+  <si>
+    <t>Measures the risk of exposing sensitive or private data in model outputs.</t>
+  </si>
+  <si>
+    <t>Stereotype Bias</t>
+  </si>
+  <si>
+    <t>Evaluates whether the model exhibits or reinforces stereotypical associations across demographic or social groups.</t>
+  </si>
+  <si>
+    <t>Disparagement Bias</t>
+  </si>
+  <si>
+    <t>Measures the extent to which the model generates harmful or offensive content targeting specific groups.</t>
+  </si>
+  <si>
+    <t>Preference Bias</t>
+  </si>
+  <si>
+    <t>Assesses whether the model exhibits biased preferences between groups or viewpoints when presented with alternatives.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1245,12 +1232,17 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1273,7 +1265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1291,6 +1283,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3139,13 +3148,13 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1162050</xdr:colOff>
+      <xdr:colOff>1187450</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:rowOff>11112</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1561966" cy="384080"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -3159,7 +3168,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12439650" y="7805737"/>
+              <a:off x="17049750" y="7910512"/>
               <a:ext cx="1561966" cy="384080"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3385,7 +3394,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="7" name="TextBox 6">
@@ -3399,7 +3408,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12439650" y="7805737"/>
+              <a:off x="17049750" y="7910512"/>
               <a:ext cx="1561966" cy="384080"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3427,6 +3436,7 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
+              <a:pPr/>
               <a:r>
                 <a:rPr lang="en-US" sz="1100" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -3634,499 +3644,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2025426" cy="475964"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB70F2D3-C7F1-F4A7-B57A-00677872367B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15249525" y="8720137"/>
-              <a:ext cx="2025426" cy="475964"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Data</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Completeness</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>1</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑁</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑖</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>=1</m:t>
-                        </m:r>
-                      </m:sub>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑁</m:t>
-                        </m:r>
-                      </m:sup>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝛾</m:t>
-                        </m:r>
-                        <m:d>
-                          <m:dPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:dPr>
-                          <m:e>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑑</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑖</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:e>
-                        </m:d>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="10" name="TextBox 9">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB70F2D3-C7F1-F4A7-B57A-00677872367B}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15249525" y="8720137"/>
-              <a:ext cx="2025426" cy="475964"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>"Data Completeness"=1/𝑁 ∑24_(𝑖=1)^𝑁▒𝛾(𝑑_𝑖 ) </a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1323975</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2046458" cy="346570"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FCDEEB-3048-96BC-E07E-5AE09064BEEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15220950" y="9367837"/>
-              <a:ext cx="2046458" cy="346570"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Data</m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t> </m:t>
-                    </m:r>
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Correctness</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>1</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>1+</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑑</m:t>
-                        </m:r>
-                        <m:d>
-                          <m:dPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:dPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝜔</m:t>
-                            </m:r>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>,</m:t>
-                            </m:r>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝜔</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑚</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:e>
-                        </m:d>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="14" name="TextBox 13">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4FCDEEB-3048-96BC-E07E-5AE09064BEEB}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15220950" y="9367837"/>
-              <a:ext cx="2046458" cy="346570"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>"Data Correctness"=1/(1+𝑑(𝜔,𝜔_𝑚 ) )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
       <xdr:colOff>1724025</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>242887</xdr:rowOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="65" cy="172227"/>
     <xdr:sp macro="" textlink="">
@@ -4179,1016 +3699,8 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1895475</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="834587" cy="678904"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F673B7-E80B-F33C-D0D8-4BF301EEA64D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15792450" y="9863137"/>
-              <a:ext cx="834587" cy="678904"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑡</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:acc>
-                          <m:accPr>
-                            <m:chr m:val="̅"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:accPr>
-                          <m:e>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>1</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:e>
-                        </m:acc>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>−</m:t>
-                        </m:r>
-                        <m:acc>
-                          <m:accPr>
-                            <m:chr m:val="̅"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:accPr>
-                          <m:e>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>2</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:e>
-                        </m:acc>
-                      </m:num>
-                      <m:den>
-                        <m:rad>
-                          <m:radPr>
-                            <m:degHide m:val="on"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:radPr>
-                          <m:deg/>
-                          <m:e>
-                            <m:f>
-                              <m:fPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:fPr>
-                              <m:num>
-                                <m:sSubSup>
-                                  <m:sSubSupPr>
-                                    <m:ctrlPr>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                    </m:ctrlPr>
-                                  </m:sSubSupPr>
-                                  <m:e>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>𝑠</m:t>
-                                    </m:r>
-                                  </m:e>
-                                  <m:sub>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>1</m:t>
-                                    </m:r>
-                                  </m:sub>
-                                  <m:sup>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>2</m:t>
-                                    </m:r>
-                                  </m:sup>
-                                </m:sSubSup>
-                              </m:num>
-                              <m:den>
-                                <m:sSub>
-                                  <m:sSubPr>
-                                    <m:ctrlPr>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                    </m:ctrlPr>
-                                  </m:sSubPr>
-                                  <m:e>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>𝑛</m:t>
-                                    </m:r>
-                                  </m:e>
-                                  <m:sub>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>1</m:t>
-                                    </m:r>
-                                  </m:sub>
-                                </m:sSub>
-                              </m:den>
-                            </m:f>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>+</m:t>
-                            </m:r>
-                            <m:f>
-                              <m:fPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:fPr>
-                              <m:num>
-                                <m:sSubSup>
-                                  <m:sSubSupPr>
-                                    <m:ctrlPr>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                    </m:ctrlPr>
-                                  </m:sSubSupPr>
-                                  <m:e>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>𝑠</m:t>
-                                    </m:r>
-                                  </m:e>
-                                  <m:sub>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>2</m:t>
-                                    </m:r>
-                                  </m:sub>
-                                  <m:sup>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>2</m:t>
-                                    </m:r>
-                                  </m:sup>
-                                </m:sSubSup>
-                              </m:num>
-                              <m:den>
-                                <m:sSub>
-                                  <m:sSubPr>
-                                    <m:ctrlPr>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                    </m:ctrlPr>
-                                  </m:sSubPr>
-                                  <m:e>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>𝑛</m:t>
-                                    </m:r>
-                                  </m:e>
-                                  <m:sub>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>2</m:t>
-                                    </m:r>
-                                  </m:sub>
-                                </m:sSub>
-                              </m:den>
-                            </m:f>
-                          </m:e>
-                        </m:rad>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="20" name="TextBox 19">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5F673B7-E80B-F33C-D0D8-4BF301EEA64D}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15792450" y="9863137"/>
-              <a:ext cx="834587" cy="678904"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝑡=((𝑥_1 ) ̅−(𝑥_2 ) ̅)/√((𝑠_1^2)/𝑛_1 +(𝑠_2^2)/𝑛_2 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1800225</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1185133" cy="479362"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74B24FFD-63CF-5070-527B-3EAF138647E0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15697200" y="10663237"/>
-              <a:ext cx="1185133" cy="479362"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSup>
-                      <m:sSupPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSupPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝜒</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>2</m:t>
-                        </m:r>
-                      </m:sup>
-                    </m:sSup>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑖</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>=1</m:t>
-                        </m:r>
-                      </m:sub>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑘</m:t>
-                        </m:r>
-                      </m:sup>
-                      <m:e>
-                        <m:f>
-                          <m:fPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:fPr>
-                          <m:num>
-                            <m:sSup>
-                              <m:sSupPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSupPr>
-                              <m:e>
-                                <m:d>
-                                  <m:dPr>
-                                    <m:ctrlPr>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                    </m:ctrlPr>
-                                  </m:dPr>
-                                  <m:e>
-                                    <m:sSub>
-                                      <m:sSubPr>
-                                        <m:ctrlPr>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                        </m:ctrlPr>
-                                      </m:sSubPr>
-                                      <m:e>
-                                        <m:r>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                          <m:t>𝑂</m:t>
-                                        </m:r>
-                                      </m:e>
-                                      <m:sub>
-                                        <m:r>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                          <m:t>𝑖</m:t>
-                                        </m:r>
-                                      </m:sub>
-                                    </m:sSub>
-                                    <m:r>
-                                      <a:rPr lang="en-US" sz="1100" i="1">
-                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                      </a:rPr>
-                                      <m:t>−</m:t>
-                                    </m:r>
-                                    <m:sSub>
-                                      <m:sSubPr>
-                                        <m:ctrlPr>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                        </m:ctrlPr>
-                                      </m:sSubPr>
-                                      <m:e>
-                                        <m:r>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                          <m:t>𝐸</m:t>
-                                        </m:r>
-                                      </m:e>
-                                      <m:sub>
-                                        <m:r>
-                                          <a:rPr lang="en-US" sz="1100" i="1">
-                                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                          </a:rPr>
-                                          <m:t>𝑖</m:t>
-                                        </m:r>
-                                      </m:sub>
-                                    </m:sSub>
-                                  </m:e>
-                                </m:d>
-                              </m:e>
-                              <m:sup>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>2</m:t>
-                                </m:r>
-                              </m:sup>
-                            </m:sSup>
-                          </m:num>
-                          <m:den>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝐸</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑖</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:den>
-                        </m:f>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="21" name="TextBox 20">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{74B24FFD-63CF-5070-527B-3EAF138647E0}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15697200" y="10663237"/>
-              <a:ext cx="1185133" cy="479362"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝜒^2=∑24_(𝑖=1)^𝑘▒(𝑂_𝑖−𝐸_𝑖 )^2/𝐸_𝑖 </a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1943100</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>214312</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1677895" cy="249940"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="TextBox 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{359CA17A-EF5F-3CAB-367F-146F5E5A7BEE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15840075" y="11615737"/>
-              <a:ext cx="1677895" cy="249940"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:sSub>
-                      <m:sSubPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:sSubPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐷</m:t>
-                        </m:r>
-                      </m:e>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑛</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>,</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑚</m:t>
-                        </m:r>
-                      </m:sub>
-                    </m:sSub>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:func>
-                      <m:funcPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:funcPr>
-                      <m:fName>
-                        <m:limLow>
-                          <m:limLowPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:limLowPr>
-                          <m:e>
-                            <m:r>
-                              <m:rPr>
-                                <m:sty m:val="p"/>
-                              </m:rPr>
-                              <a:rPr lang="en-US" sz="1100" i="0">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>sup</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:lim>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑥</m:t>
-                            </m:r>
-                          </m:lim>
-                        </m:limLow>
-                      </m:fName>
-                      <m:e>
-                        <m:d>
-                          <m:dPr>
-                            <m:begChr m:val="|"/>
-                            <m:endChr m:val="|"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:dPr>
-                          <m:e>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝐹</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑛</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                            <m:d>
-                              <m:dPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:dPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                            </m:d>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>−</m:t>
-                            </m:r>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝐺</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑚</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                            <m:d>
-                              <m:dPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:dPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                            </m:d>
-                          </m:e>
-                        </m:d>
-                      </m:e>
-                    </m:func>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="TextBox 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{359CA17A-EF5F-3CAB-367F-146F5E5A7BEE}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15840075" y="11615737"/>
-              <a:ext cx="1677895" cy="249940"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>𝐷_(𝑛,𝑚)=sup_𝑥⁡|𝐹_𝑛 (𝑥)−𝐺_𝑚 (𝑥)|</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
       <xdr:colOff>1352550</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1969385" cy="321435"/>
@@ -5415,537 +3927,6 @@
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
                 <a:t>"MTBF"="Total Operational Time" /"Number of Failures" </a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>1247775</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2444515" cy="475515"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="TextBox 23">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{579CFE3D-7430-B1D4-A2ED-E1DB472941E3}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15144750" y="13930312"/>
-              <a:ext cx="2444515" cy="475515"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Repeatability</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=1−</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>1</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑛</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>−1</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                    <m:nary>
-                      <m:naryPr>
-                        <m:chr m:val="∑"/>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:naryPr>
-                      <m:sub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑖</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>=1</m:t>
-                        </m:r>
-                      </m:sub>
-                      <m:sup>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑛</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>−1</m:t>
-                        </m:r>
-                      </m:sup>
-                      <m:e>
-                        <m:d>
-                          <m:dPr>
-                            <m:begChr m:val="|"/>
-                            <m:endChr m:val="|"/>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:dPr>
-                          <m:e>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑖</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>−</m:t>
-                            </m:r>
-                            <m:sSub>
-                              <m:sSubPr>
-                                <m:ctrlPr>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                </m:ctrlPr>
-                              </m:sSubPr>
-                              <m:e>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑥</m:t>
-                                </m:r>
-                              </m:e>
-                              <m:sub>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>𝑖</m:t>
-                                </m:r>
-                                <m:r>
-                                  <a:rPr lang="en-US" sz="1100" i="1">
-                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                                  </a:rPr>
-                                  <m:t>+1</m:t>
-                                </m:r>
-                              </m:sub>
-                            </m:sSub>
-                          </m:e>
-                        </m:d>
-                      </m:e>
-                    </m:nary>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="24" name="TextBox 23">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{579CFE3D-7430-B1D4-A2ED-E1DB472941E3}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="15144750" y="13930312"/>
-              <a:ext cx="2444515" cy="475515"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>"Repeatability"=1−1/(𝑛−1) ∑24_(𝑖=1)^(𝑛−1)▒|𝑥_𝑖−𝑥_(𝑖+1) | </a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>223837</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="5445401" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C953BC92-5EDB-F931-3D37-AF0B1657FE6C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14620875" y="14673262"/>
-              <a:ext cx="5445401" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>\</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑡𝑒𝑥𝑡</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>{</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑅𝑒𝑝𝑟𝑜𝑑𝑢𝑐𝑖𝑏𝑖𝑙𝑖𝑡𝑦</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>} = 1 − \</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑓𝑟𝑎𝑐</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>{\</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑚𝑎𝑡h𝑟𝑚</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>{</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑉𝑎𝑟</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>}(\</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>h𝑎𝑡</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>{</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑦</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>})}{\</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑚𝑎𝑡h𝑟𝑚</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>{</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑉𝑎𝑟</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>}_{\</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑚𝑎𝑥</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>}}</m:t>
-                    </m:r>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="8" name="TextBox 7">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C953BC92-5EDB-F931-3D37-AF0B1657FE6C}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="14620875" y="14673262"/>
-              <a:ext cx="5445401" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>\𝑡𝑒𝑥𝑡{𝑅𝑒𝑝𝑟𝑜𝑑𝑢𝑐𝑖𝑏𝑖𝑙𝑖𝑡𝑦} = 1 - \𝑓𝑟𝑎𝑐{\𝑚𝑎𝑡ℎ𝑟𝑚{𝑉𝑎𝑟}(\ℎ𝑎𝑡{𝑦})}{\𝑚𝑎𝑡ℎ𝑟𝑚{𝑉𝑎𝑟}_{\𝑚𝑎𝑥}}</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -9277,19 +7258,75 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
+      <xdr:colOff>634524</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>204787</xdr:rowOff>
+      <xdr:rowOff>197993</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1240276" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD60CDC8-A4AB-542D-5255-1533543DE813}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14668024" y="5252593"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0"/>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2063129" cy="224549"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A10BCC15-4EEE-3A72-C4AF-9060025D2D3F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C2E9EC9-C300-A4B7-32A3-EE81044FBC02}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9297,8 +7334,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13011150" y="5348287"/>
-              <a:ext cx="1240276" cy="173766"/>
+              <a:off x="14503400" y="5156200"/>
+              <a:ext cx="2063129" cy="224549"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9325,7 +7362,6 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
@@ -9336,13 +7372,7 @@
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>|</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝑓</m:t>
+                      <m:t>𝐹</m:t>
                     </m:r>
                     <m:d>
                       <m:dPr>
@@ -9357,65 +7387,196 @@
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>𝑥</m:t>
+                          <m:t>𝑓</m:t>
                         </m:r>
                         <m:r>
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>\</m:t>
-                        </m:r>
-                        <m:r>
-                          <m:rPr>
-                            <m:sty m:val="p"/>
-                          </m:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:r>
                           <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
-                          <m:t>S</m:t>
-                        </m:r>
+                          <m:t>𝑔</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>,</m:t>
+                        </m:r>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑁</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
                       </m:e>
                     </m:d>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>−</m:t>
+                      <m:t>=</m:t>
                     </m:r>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>𝑓</m:t>
-                    </m:r>
-                    <m:d>
-                      <m:dPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:dPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑥</m:t>
-                        </m:r>
-                      </m:e>
-                    </m:d>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>|&gt;</m:t>
+                      <m:t>𝐸</m:t>
                     </m:r>
                     <m:r>
                       <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>𝛿</m:t>
+                      <m:t>[</m:t>
+                    </m:r>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑔</m:t>
+                            </m:r>
+                            <m:d>
+                              <m:dPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:dPr>
+                              <m:e>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑥</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>′</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:e>
+                            </m:d>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑓</m:t>
+                            </m:r>
+                            <m:d>
+                              <m:dPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:dPr>
+                              <m:e>
+                                <m:sSup>
+                                  <m:sSupPr>
+                                    <m:ctrlPr>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                    </m:ctrlPr>
+                                  </m:sSupPr>
+                                  <m:e>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>𝑥</m:t>
+                                    </m:r>
+                                  </m:e>
+                                  <m:sup>
+                                    <m:r>
+                                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                      </a:rPr>
+                                      <m:t>′</m:t>
+                                    </m:r>
+                                  </m:sup>
+                                </m:sSup>
+                              </m:e>
+                            </m:d>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>]</m:t>
                     </m:r>
                   </m:oMath>
                 </m:oMathPara>
@@ -9425,13 +7586,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="3" name="TextBox 2">
+            <xdr:cNvPr id="12" name="TextBox 11">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A10BCC15-4EEE-3A72-C4AF-9060025D2D3F}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C2E9EC9-C300-A4B7-32A3-EE81044FBC02}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9439,8 +7600,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="13011150" y="5348287"/>
-              <a:ext cx="1240276" cy="173766"/>
+              <a:off x="14503400" y="5156200"/>
+              <a:ext cx="2063129" cy="224549"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9471,7 +7632,7 @@
                 <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>|𝑓(𝑥\S)−𝑓(𝑥)|&gt;𝛿</a:t>
+                <a:t>𝐹(𝑓,𝑔,𝑁_𝑥 )=𝐸[(𝑔(𝑥^′ )−𝑓(𝑥^′ ))^2]</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -9484,19 +7645,19 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:colOff>717550</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1532920" cy="340799"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
+    <xdr:ext cx="1207638" cy="321563"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3861BAE5-7FFC-6A4C-A81F-AC76BEA48C1B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F86BED72-18F3-22E7-B380-41CCF4F5B976}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9504,8 +7665,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12753975" y="5738812"/>
-              <a:ext cx="1532920" cy="340799"/>
+              <a:off x="14751050" y="5511800"/>
+              <a:ext cx="1207638" cy="321563"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9532,122 +7693,142 @@
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
                   <m:oMathParaPr>
                     <m:jc m:val="centerGroup"/>
                   </m:oMathParaPr>
                   <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>1</m:t>
+                            </m:r>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑁</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:d>
                     <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
+                      <a:rPr lang="en-US" sz="1100" b="0" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                       </a:rPr>
-                      <m:t>Faithfulness</m:t>
+                      <m:t>∑</m:t>
                     </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=−</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
+                    <m:d>
+                      <m:dPr>
                         <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
+                      </m:dPr>
+                      <m:e>
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝜎</m:t>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑦</m:t>
                             </m:r>
                           </m:e>
                           <m:sub>
                             <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑥𝑦</m:t>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
                             </m:r>
                           </m:sub>
                         </m:sSub>
-                      </m:num>
-                      <m:den>
+                        <m:r>
+                          <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−</m:t>
+                        </m:r>
                         <m:sSub>
                           <m:sSubPr>
                             <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
                                 <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                               </a:rPr>
                             </m:ctrlPr>
                           </m:sSubPr>
                           <m:e>
                             <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝜎</m:t>
+                              <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑦</m:t>
                             </m:r>
                           </m:e>
                           <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑥</m:t>
-                            </m:r>
+                            <m:d>
+                              <m:dPr>
+                                <m:begChr m:val="{"/>
+                                <m:endChr m:val="}"/>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:dPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑥</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑎</m:t>
+                                </m:r>
+                              </m:e>
+                            </m:d>
                           </m:sub>
                         </m:sSub>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>+</m:t>
-                        </m:r>
-                        <m:sSub>
-                          <m:sSubPr>
-                            <m:ctrlPr>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                            </m:ctrlPr>
-                          </m:sSubPr>
-                          <m:e>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝜎</m:t>
-                            </m:r>
-                          </m:e>
-                          <m:sub>
-                            <m:r>
-                              <a:rPr lang="en-US" sz="1100" i="1">
-                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                              </a:rPr>
-                              <m:t>𝑦</m:t>
-                            </m:r>
-                          </m:sub>
-                        </m:sSub>
-                      </m:den>
-                    </m:f>
+                      </m:e>
+                    </m:d>
                   </m:oMath>
                 </m:oMathPara>
               </a14:m>
@@ -9656,13 +7837,13 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback xmlns="">
+      <mc:Fallback>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="TextBox 3">
+            <xdr:cNvPr id="15" name="TextBox 14">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3861BAE5-7FFC-6A4C-A81F-AC76BEA48C1B}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F86BED72-18F3-22E7-B380-41CCF4F5B976}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -9670,8 +7851,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="12753975" y="5738812"/>
-              <a:ext cx="1532920" cy="340799"/>
+              <a:off x="14751050" y="5511800"/>
+              <a:ext cx="1207638" cy="321563"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -9699,356 +7880,10 @@
             <a:lstStyle/>
             <a:p>
               <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
+                <a:rPr lang="en-US" sz="1100" b="0" i="0">
                   <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                 </a:rPr>
-                <a:t>"Faithfulness"=−𝜎_𝑥𝑦/(𝜎_𝑥+𝜎_𝑦 )</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>204787</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1426031" cy="173766"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0520BCC8-C8BC-09D6-E3A1-6C94D8A696A8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12868275" y="6300787"/>
-              <a:ext cx="1426031" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Monotonicity</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>𝜌</m:t>
-                    </m:r>
-                    <m:d>
-                      <m:dPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:dPr>
-                      <m:e>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑥</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>,</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑦</m:t>
-                        </m:r>
-                      </m:e>
-                    </m:d>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="5" name="TextBox 4">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0520BCC8-C8BC-09D6-E3A1-6C94D8A696A8}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12868275" y="6300787"/>
-              <a:ext cx="1426031" cy="173766"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>"Monotonicity"=𝜌(𝑥,𝑦)</a:t>
-              </a:r>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1379287" cy="319703"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-      <mc:Choice Requires="a14">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92A420F3-EDBC-00F5-A968-BDAD62F27215}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12858750" y="7291387"/>
-              <a:ext cx="1379287" cy="319703"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr/>
-              <a14:m>
-                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                    <m:r>
-                      <m:rPr>
-                        <m:nor/>
-                      </m:rPr>
-                      <a:rPr lang="en-US" sz="1100" i="0">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>Sensitivity</m:t>
-                    </m:r>
-                    <m:r>
-                      <a:rPr lang="en-US" sz="1100" i="1">
-                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                      </a:rPr>
-                      <m:t>=</m:t>
-                    </m:r>
-                    <m:f>
-                      <m:fPr>
-                        <m:ctrlPr>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                        </m:ctrlPr>
-                      </m:fPr>
-                      <m:num>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇𝑃</m:t>
-                        </m:r>
-                      </m:num>
-                      <m:den>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝑇𝑃</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>+</m:t>
-                        </m:r>
-                        <m:r>
-                          <a:rPr lang="en-US" sz="1100" i="1">
-                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                          </a:rPr>
-                          <m:t>𝐹𝑁</m:t>
-                        </m:r>
-                      </m:den>
-                    </m:f>
-                  </m:oMath>
-                </m:oMathPara>
-              </a14:m>
-              <a:endParaRPr lang="en-US" sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Choice>
-      <mc:Fallback xmlns="">
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="6" name="TextBox 5">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92A420F3-EDBC-00F5-A968-BDAD62F27215}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="12858750" y="7291387"/>
-              <a:ext cx="1379287" cy="319703"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="tx1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-US" sz="1100" i="0">
-                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
-                </a:rPr>
-                <a:t>"Sensitivity"=𝑇𝑃/(𝑇𝑃+𝐹𝑁)</a:t>
+                <a:t>(1/𝑁)∑(𝑦_𝑥−𝑦_{𝑥│𝑎}  )</a:t>
               </a:r>
               <a:endParaRPr lang="en-US" sz="1100"/>
             </a:p>
@@ -14253,19 +12088,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7EA8B98-5611-4551-B3EB-7958DD4CE8C9}">
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.5703125" customWidth="1"/>
-    <col min="2" max="3" width="11.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" customWidth="1"/>
-    <col min="7" max="7" width="109.7109375" customWidth="1"/>
-    <col min="8" max="8" width="95.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.5" customWidth="1"/>
+    <col min="2" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="14.1640625" customWidth="1"/>
+    <col min="6" max="6" width="18.33203125" customWidth="1"/>
+    <col min="7" max="7" width="109.6640625" customWidth="1"/>
+    <col min="8" max="8" width="95.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14291,7 +12126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="36.75" customHeight="1">
+    <row r="2" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -14315,7 +12150,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -14341,7 +12176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -14367,7 +12202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -14393,7 +12228,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -14419,7 +12254,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -14445,7 +12280,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -14471,7 +12306,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -14497,7 +12332,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -14523,7 +12358,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -14549,7 +12384,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="45">
+    <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -14575,7 +12410,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="60">
+    <row r="13" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
@@ -14598,7 +12433,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="45">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>59</v>
       </c>
@@ -14624,7 +12459,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -14648,7 +12483,7 @@
       </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -14674,7 +12509,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="75">
+    <row r="17" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>72</v>
       </c>
@@ -14697,7 +12532,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45">
+    <row r="18" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>74</v>
       </c>
@@ -14721,7 +12556,7 @@
       </c>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="30">
+    <row r="19" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>76</v>
       </c>
@@ -14747,7 +12582,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30">
+    <row r="20" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>79</v>
       </c>
@@ -14771,7 +12606,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" ht="45">
+    <row r="21" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -14794,7 +12629,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="46.5" customHeight="1">
+    <row r="22" spans="1:8" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>84</v>
       </c>
@@ -14807,16 +12642,22 @@
       <c r="D22" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="E22" s="9" t="s">
+        <v>57</v>
+      </c>
       <c r="F22" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="H22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="45">
-      <c r="A23" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>85</v>
@@ -14827,56 +12668,74 @@
       <c r="D23" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="E23" s="9" t="s">
+        <v>57</v>
+      </c>
       <c r="F23" t="s">
         <v>37</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>310</v>
+      </c>
+      <c r="H23" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="64.5" customHeight="1">
-      <c r="A24" t="s">
-        <v>89</v>
-      </c>
-      <c r="B24" s="5" t="s">
+    <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F24" t="s">
-        <v>90</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
+      <c r="E24" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>308</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="60">
-      <c r="A25" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="5" t="s">
+    <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B25" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F25" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>94</v>
+      <c r="E25" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="60">
-      <c r="A26" t="s">
-        <v>95</v>
+    <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>85</v>
@@ -14885,18 +12744,24 @@
         <v>10</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="F26" t="s">
         <v>37</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>96</v>
+        <v>313</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="45">
+    <row r="27" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>85</v>
@@ -14904,194 +12769,328 @@
       <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>11</v>
+      <c r="D27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="F27" t="s">
         <v>37</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>98</v>
+        <v>314</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="45">
-      <c r="A28" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F28" t="s">
+      <c r="E28" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>102</v>
+      <c r="G29" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="45">
-      <c r="A29" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B29" s="5" t="s">
+    <row r="30" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F29" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>104</v>
+      <c r="D30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="H30" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="45">
-      <c r="A30" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="1" t="s">
+    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F30" t="s">
+      <c r="D31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>106</v>
+      <c r="G37" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="45">
-      <c r="A31" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31" t="s">
-        <v>37</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>108</v>
+    <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>336</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30">
-      <c r="A32" t="s">
-        <v>109</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" t="s">
+    <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F32" t="s">
-        <v>37</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H32" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="30">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>37</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H33" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" t="s">
-        <v>111</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>37</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H34" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>37</v>
-      </c>
-      <c r="G35" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" t="s">
+      <c r="F39" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -15104,17 +13103,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{622D72B4-C396-4A69-8B25-0431119628AF}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="5" width="13.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="82.28515625" customWidth="1"/>
-    <col min="8" max="8" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="28.5" customWidth="1"/>
+    <col min="2" max="5" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" customWidth="1"/>
+    <col min="7" max="7" width="82.33203125" customWidth="1"/>
+    <col min="8" max="8" width="36.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15140,9 +13139,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -15151,24 +13150,24 @@
         <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="H2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -15183,18 +13182,18 @@
         <v>57</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -15209,18 +13208,18 @@
         <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="H4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -15235,117 +13234,169 @@
         <v>57</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="H5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="H6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" t="s">
-        <v>136</v>
-      </c>
-      <c r="H7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" t="s">
-        <v>110</v>
-      </c>
-      <c r="C8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" t="s">
-        <v>138</v>
-      </c>
-      <c r="H8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="30">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="H9" t="s">
-        <v>71</v>
+      <c r="G11" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -15356,17 +13407,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B9872C0-87ED-4942-9D20-BE02F97DE3C1}">
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" customWidth="1"/>
-    <col min="2" max="5" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="5" width="14.5" customWidth="1"/>
     <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="82.28515625" customWidth="1"/>
-    <col min="8" max="8" width="48.5703125" customWidth="1"/>
+    <col min="7" max="7" width="82.33203125" customWidth="1"/>
+    <col min="8" max="8" width="48.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15377,7 +13428,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -15392,9 +13443,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -15403,24 +13454,24 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>26</v>
@@ -15429,24 +13480,24 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>26</v>
@@ -15455,27 +13506,27 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="45">
+    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -15490,19 +13541,19 @@
         <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
@@ -15514,19 +13565,19 @@
         <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" ht="60">
+    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
@@ -15538,16 +13589,16 @@
         <v>33</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" spans="1:8" ht="60">
+    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -15562,16 +13613,16 @@
         <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" spans="1:8" ht="105">
+    <row r="9" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>10</v>
@@ -15586,13 +13637,13 @@
         <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" ht="45">
+    <row r="10" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>50</v>
@@ -15604,19 +13655,19 @@
         <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="H10" s="1"/>
     </row>
-    <row r="11" spans="1:8" ht="60">
+    <row r="11" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>136</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -15631,22 +13682,22 @@
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>165</v>
+        <v>137</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="H11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="45">
+    <row r="12" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>27</v>
@@ -15658,13 +13709,13 @@
         <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="H12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="60">
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>50</v>
@@ -15682,15 +13733,15 @@
         <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="45">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>50</v>
@@ -15705,93 +13756,93 @@
         <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>172</v>
+        <v>144</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="G15" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30">
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="75">
+    <row r="17" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>180</v>
+        <v>152</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>56</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="45">
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>154</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>55</v>
@@ -15806,18 +13857,18 @@
         <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="45">
+    <row r="19" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>82</v>
@@ -15835,85 +13886,163 @@
         <v>37</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="72.75">
-      <c r="A21" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>37</v>
-      </c>
-      <c r="G21" t="s">
-        <v>190</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>192</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22" t="s">
-        <v>111</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" t="s">
-        <v>193</v>
-      </c>
-      <c r="H22" t="s">
-        <v>71</v>
+      <c r="G25" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -15926,16 +14055,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD31DF0-270A-4D26-B4BC-9FB8557FE966}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" customWidth="1"/>
-    <col min="2" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
-    <col min="7" max="7" width="86.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" customWidth="1"/>
+    <col min="2" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" customWidth="1"/>
+    <col min="7" max="7" width="86.5" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15961,9 +14090,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>26</v>
@@ -15975,24 +14104,24 @@
         <v>56</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="45">
+    <row r="3" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
@@ -16001,21 +14130,21 @@
         <v>56</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
@@ -16024,24 +14153,24 @@
         <v>56</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -16050,50 +14179,50 @@
         <v>56</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="45">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F6" t="s">
-        <v>207</v>
+        <v>173</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>208</v>
+        <v>174</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>209</v>
+        <v>175</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
@@ -16105,18 +14234,18 @@
         <v>12</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="G7" t="s">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>50</v>
@@ -16131,18 +14260,18 @@
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G8" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>50</v>
@@ -16157,18 +14286,18 @@
         <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>50</v>
@@ -16183,18 +14312,18 @@
         <v>12</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>50</v>
@@ -16209,18 +14338,18 @@
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G11" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>185</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>50</v>
@@ -16235,18 +14364,18 @@
         <v>12</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45">
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>187</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>50</v>
@@ -16261,10 +14390,10 @@
         <v>12</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>222</v>
+        <v>188</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>71</v>
@@ -16277,19 +14406,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AC02F5-2786-470A-8C62-E1E8EFDA7700}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" customWidth="1"/>
-    <col min="2" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
-    <col min="7" max="7" width="82.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.5" customWidth="1"/>
+    <col min="2" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.5" customWidth="1"/>
+    <col min="7" max="7" width="82.33203125" customWidth="1"/>
     <col min="8" max="8" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16315,9 +14444,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -16326,24 +14455,24 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="G2" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -16352,24 +14481,24 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>229</v>
+        <v>195</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -16378,27 +14507,27 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
@@ -16410,21 +14539,21 @@
         <v>57</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>235</v>
+        <v>201</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
@@ -16436,47 +14565,47 @@
         <v>57</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="45">
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -16485,21 +14614,21 @@
         <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G8" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="60">
+    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
@@ -16514,18 +14643,18 @@
         <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30">
+    <row r="10" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>217</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
@@ -16537,21 +14666,21 @@
         <v>11</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>253</v>
+        <v>219</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>254</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
@@ -16563,21 +14692,21 @@
         <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>257</v>
+        <v>223</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>224</v>
       </c>
       <c r="B12" t="s">
         <v>55</v>
@@ -16586,7 +14715,7 @@
         <v>10</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>28</v>
@@ -16595,15 +14724,15 @@
         <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>259</v>
+        <v>225</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45">
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>226</v>
       </c>
       <c r="B13" t="s">
         <v>82</v>
@@ -16612,7 +14741,7 @@
         <v>10</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -16621,78 +14750,157 @@
         <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>261</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="45">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="D14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>264</v>
+      <c r="B16" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30">
-      <c r="A15" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" s="4" t="s">
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>266</v>
+      <c r="C17" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="90">
-      <c r="A16" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>269</v>
+      <c r="C18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45">
-      <c r="A17" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B17" s="4" t="s">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>271</v>
+      <c r="D19" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -16704,16 +14912,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4534AC4-4849-4F7D-9BF9-260BE31EF745}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="2" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="82" customWidth="1"/>
-    <col min="8" max="8" width="82.42578125" customWidth="1"/>
+    <col min="8" max="8" width="82.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16739,9 +14947,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -16756,18 +14964,18 @@
         <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -16782,18 +14990,18 @@
         <v>57</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="30">
+    <row r="4" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -16808,18 +15016,18 @@
         <v>57</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -16828,24 +15036,24 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -16857,21 +15065,21 @@
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="45">
+    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
@@ -16880,30 +15088,30 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>161</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="45">
+    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -16915,21 +15123,21 @@
         <v>33</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30">
+    <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -16941,21 +15149,21 @@
         <v>33</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>289</v>
+        <v>250</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="60">
+    <row r="10" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>290</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -16967,18 +15175,18 @@
         <v>33</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>291</v>
+        <v>252</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>292</v>
+        <v>253</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>11</v>
@@ -16987,18 +15195,18 @@
         <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="G11" t="s">
-        <v>294</v>
+        <v>255</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="45">
+    <row r="12" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>50</v>
@@ -17016,291 +15224,223 @@
         <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>296</v>
+        <v>257</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45">
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>297</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>238</v>
+        <v>204</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>298</v>
+        <v>259</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>299</v>
+        <v>260</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G14" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="45">
+    <row r="15" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="B15" t="s">
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>302</v>
+        <v>263</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30">
+    <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G16" t="s">
-        <v>304</v>
+        <v>265</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="45">
+    <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30">
+    <row r="18" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>308</v>
+        <v>269</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>309</v>
+        <v>270</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="2" t="s">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F19" t="s">
-        <v>311</v>
-      </c>
-      <c r="G19" t="s">
-        <v>312</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="F19" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
-        <v>313</v>
-      </c>
-      <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" s="2" t="s">
+    <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F20" t="s">
-        <v>314</v>
-      </c>
-      <c r="G20" t="s">
-        <v>315</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="F20" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="29.25">
-      <c r="A21" t="s">
-        <v>316</v>
-      </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" t="s">
-        <v>111</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" t="s">
-        <v>314</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H21" t="s">
-        <v>71</v>
-      </c>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D21" s="2"/>
+      <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>318</v>
-      </c>
-      <c r="B22" t="s">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>314</v>
-      </c>
-      <c r="G22" t="s">
-        <v>320</v>
-      </c>
-      <c r="H22" t="s">
-        <v>71</v>
-      </c>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:8">
-      <c r="A23" t="s">
-        <v>321</v>
-      </c>
-      <c r="B23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" t="s">
-        <v>319</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" t="s">
-        <v>314</v>
-      </c>
-      <c r="G23" t="s">
-        <v>322</v>
-      </c>
-      <c r="H23" t="s">
-        <v>71</v>
-      </c>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D23" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17311,18 +15451,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E85A7E7-1F88-48B7-8A47-A844F306AD2E}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="5" width="9.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" customWidth="1"/>
+    <col min="1" max="1" width="27.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="5" width="9.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.1640625" customWidth="1"/>
     <col min="7" max="7" width="101" customWidth="1"/>
-    <col min="8" max="8" width="81.7109375" customWidth="1"/>
+    <col min="8" max="8" width="81.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17336,7 +15476,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>323</v>
+        <v>272</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -17348,9 +15488,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -17365,18 +15505,18 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="G2" t="s">
-        <v>325</v>
+        <v>274</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>326</v>
+        <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="30">
+    <row r="3" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>276</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -17391,50 +15531,50 @@
         <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>329</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="60">
+    <row r="4" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>331</v>
+        <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="45">
+    <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="B5" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -17443,15 +15583,15 @@
         <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>333</v>
+        <v>282</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="60">
+    <row r="6" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
         <v>10</v>
@@ -17460,27 +15600,27 @@
         <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="90">
+    <row r="7" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="B7" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C7" t="s">
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E7" t="s">
         <v>12</v>
@@ -17489,21 +15629,21 @@
         <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="60">
+    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>287</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
@@ -17512,21 +15652,21 @@
         <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>339</v>
+        <v>288</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="45">
+    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="B9" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
@@ -17535,12 +15675,12 @@
         <v>65</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>341</v>
+        <v>290</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="90">
+    <row r="10" spans="1:8" ht="80" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
@@ -17549,7 +15689,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>12</v>
@@ -17558,41 +15698,41 @@
         <v>33</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>343</v>
+        <v>292</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="45">
+    <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="74.25" customHeight="1">
+    <row r="12" spans="1:8" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="B12" t="s">
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
@@ -17604,18 +15744,18 @@
         <v>13</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="45">
+    <row r="13" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -17627,12 +15767,12 @@
         <v>65</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="B14" t="s">
         <v>50</v>
@@ -17650,12 +15790,12 @@
         <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="45">
+    <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
@@ -17664,7 +15804,7 @@
         <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -17673,84 +15813,84 @@
         <v>37</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" t="s">
-        <v>356</v>
-      </c>
-      <c r="B16" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" t="s">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F16" t="s">
-        <v>135</v>
-      </c>
-      <c r="G16" t="s">
-        <v>357</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="F16" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
-        <v>358</v>
-      </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F17" t="s">
-        <v>135</v>
-      </c>
-      <c r="G17" t="s">
-        <v>359</v>
-      </c>
-      <c r="H17" t="s">
-        <v>360</v>
+      <c r="F17" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
-        <v>361</v>
-      </c>
-      <c r="B18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" t="s">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F18" t="s">
-        <v>135</v>
-      </c>
-      <c r="G18" t="s">
-        <v>362</v>
-      </c>
-      <c r="H18" t="s">
+      <c r="F18" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>71</v>
       </c>
     </row>
